--- a/basedatos_partidas/salida/descompuestos/07.04.02.100.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.04.02.100.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -567,131 +567,131 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MT-AUTOM-PORTON</t>
+          <t>MT-ELECTRODO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Motor y automatismo para portón corredizo o batiente, con mandos y finales de carrera.</t>
+          <t>Electrodo revestido para soldadura estructural por arco eléctrico.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>4.8</v>
       </c>
       <c r="H11" t="n">
-        <v>180</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MT-ELECTRODO</t>
+          <t>MT-RIEL-CORRED</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Electrodo revestido para soldadura estructural por arco eléctrico.</t>
+          <t>Riel superior e inferior con carros para puerta corrediza.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>2.88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MT-RIEL-CORRED</t>
+          <t>MT-PINT-ANTICORR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>l</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Riel superior e inferior con carros para puerta corrediza.</t>
+          <t>Imprimación anticorrosiva de fondo para estructura metálica.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="H13" t="n">
-        <v>84</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MT-PINT-ANTICORR</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Imprimación anticorrosiva de fondo para estructura metálica.</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G14" t="n">
-        <v>7.2</v>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal materiales:</t>
+        </is>
       </c>
       <c r="H14" t="n">
+        <v>169.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>Equipo y maquinaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MQ-SOLDADORA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Equipo de soldadura eléctrica por arco con sus accesorios, incluida amortización y consumo.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H16" t="n">
         <v>4.32</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal materiales:</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>349.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>Equipo y maquinaria</t>
-        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MQ-SOLDADORA</t>
+          <t>MQ-TALADRO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -701,69 +701,69 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Equipo de soldadura eléctrica por arco con sus accesorios, incluida amortización y consumo.</t>
+          <t>Taladro percutor con brocas, incluida amortización y consumo.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="H17" t="n">
-        <v>4.32</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MQ-TALADRO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal equipo y maquinaria:</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Mano de obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MO-OF1-SOLD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Taladro percutor con brocas, incluida amortización y consumo.</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal equipo y maquinaria:</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>4.92</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>Mano de obra</t>
-        </is>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Oficial de 1ª soldador.</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MO-OF1-SOLD</t>
+          <t>MO-OF1-ELE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -773,23 +773,23 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Oficial de 1ª soldador.</t>
+          <t>Oficial de 1ª electricista.</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="n">
         <v>5.5</v>
       </c>
       <c r="H21" t="n">
-        <v>22</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MO-OF1-ELE</t>
+          <t>MO-AYU</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -799,100 +799,74 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Oficial de 1ª electricista.</t>
+          <t>Ayudante.</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="H22" t="n">
-        <v>8.25</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>MO-AYU</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Ayudante.</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>3.5</v>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal mano de obra:</t>
+        </is>
       </c>
       <c r="H23" t="n">
-        <v>5.6</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="24">
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal mano de obra:</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>35.85</v>
+      <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>Costes directos complementarios</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>209.97</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="26">
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Costes directos complementarios</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>389.97</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Costes directos (1+2+3+4):</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="5" t="n">
-        <v>393.87</v>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="5" t="n">
+        <v>212.07</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/07.04.02.100.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.04.02.100.xlsx
@@ -584,10 +584,10 @@
         <v>0.6</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -636,10 +636,10 @@
         <v>0.6</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>4.32</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="14">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>169.2</v>
+        <v>169.8</v>
       </c>
     </row>
     <row r="15">
@@ -847,10 +847,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>209.97</v>
+        <v>210.57</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="26">
@@ -866,7 +866,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>212.07</v>
+        <v>212.68</v>
       </c>
     </row>
   </sheetData>
